--- a/makeup_artist_forms/002_wedding_hair_and_makeup_questionnaire--makeup_artist_forms.xlsx
+++ b/makeup_artist_forms/002_wedding_hair_and_makeup_questionnaire--makeup_artist_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -712,12 +712,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>makeup_services</t>
+          <t>makeup_services_2</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Makeup Services</t>
+          <t>Makeup Services 2</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -928,7 +928,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Makeup Services</t>
+          <t>Make Up Services</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -950,12 +950,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>make_up_services</t>
+          <t>make_up_services_2</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Makeup Services</t>
+          <t>Make Up Services 2</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -982,7 +982,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Makeup Services</t>
+          <t>Make Up Services1</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -1009,7 +1009,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Makeup Services</t>
+          <t>Make Up Services2</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -1036,7 +1036,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Makeup Services</t>
+          <t>Make Up Services3</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -1063,7 +1063,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Makeup Services</t>
+          <t>Make Up Services4</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -1090,7 +1090,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Makeup Services</t>
+          <t>Make Up Services5</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -1117,7 +1117,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Makeup Services</t>
+          <t>Make Up Services6</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -1146,8 +1146,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="29" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="32" customWidth="1" min="2" max="2"/>
+    <col width="32" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1175,12 +1175,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1192,12 +1192,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -1209,12 +1209,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'haircut'}</t>
+          <t>haircut</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Haircut'}</t>
+          <t>Haircut</t>
         </is>
       </c>
     </row>
@@ -1226,12 +1226,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'color'}</t>
+          <t>color</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Color'}</t>
+          <t>Color</t>
         </is>
       </c>
     </row>
@@ -1243,12 +1243,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'style'}</t>
+          <t>style</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Style'}</t>
+          <t>Style</t>
         </is>
       </c>
     </row>
@@ -1260,12 +1260,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'extensions'}</t>
+          <t>extensions</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'Extensions'}</t>
+          <t>Extensions</t>
         </is>
       </c>
     </row>
@@ -1277,12 +1277,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_5,_'label':_'hair_accessories'}</t>
+          <t>hair_accessories</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 5, 'label': 'Hair Accessories'}</t>
+          <t>Hair Accessories</t>
         </is>
       </c>
     </row>
@@ -1294,12 +1294,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'airbrush'}</t>
+          <t>airbrush</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Airbrush'}</t>
+          <t>Airbrush</t>
         </is>
       </c>
     </row>
@@ -1311,12 +1311,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'airbrush_highlight'}</t>
+          <t>airbrush_highlight</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Airbrush Highlight'}</t>
+          <t>Airbrush Highlight</t>
         </is>
       </c>
     </row>
@@ -1328,12 +1328,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'airbrush_highlight_and_contour'}</t>
+          <t>airbrush_highlight_and_contour</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Airbrush Highlight and Contour'}</t>
+          <t>Airbrush Highlight and Contour</t>
         </is>
       </c>
     </row>
@@ -1345,12 +1345,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'airbrush_makeup'}</t>
+          <t>airbrush_makeup</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'Airbrush Makeup'}</t>
+          <t>Airbrush Makeup</t>
         </is>
       </c>
     </row>
@@ -1362,12 +1362,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'id':_5,_'label':_'bridal'}</t>
+          <t>bridal</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'id': 5, 'label': 'Bridal'}</t>
+          <t>Bridal</t>
         </is>
       </c>
     </row>
@@ -1379,12 +1379,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'id':_6,_'label':_'bridal_touch_up'}</t>
+          <t>bridal_touch_up</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'id': 6, 'label': 'Bridal Touch Up'}</t>
+          <t>Bridal Touch Up</t>
         </is>
       </c>
     </row>
@@ -1396,12 +1396,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'id':_7,_'label':_'bridal_and_contour'}</t>
+          <t>bridal_and_contour</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'id': 7, 'label': 'Bridal and Contour'}</t>
+          <t>Bridal and Contour</t>
         </is>
       </c>
     </row>
@@ -1413,12 +1413,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'id':_8,_'label':_'bridal_and_highlight'}</t>
+          <t>bridal_and_highlight</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'id': 8, 'label': 'Bridal and Highlight'}</t>
+          <t>Bridal and Highlight</t>
         </is>
       </c>
     </row>
@@ -1430,12 +1430,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'curly'}</t>
+          <t>curly</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Curly'}</t>
+          <t>Curly</t>
         </is>
       </c>
     </row>
@@ -1447,12 +1447,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'straight'}</t>
+          <t>straight</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Straight'}</t>
+          <t>Straight</t>
         </is>
       </c>
     </row>
@@ -1464,12 +1464,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'wavy'}</t>
+          <t>wavy</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Wavy'}</t>
+          <t>Wavy</t>
         </is>
       </c>
     </row>
@@ -1481,12 +1481,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'updo'}</t>
+          <t>updo</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'Updo'}</t>
+          <t>Updo</t>
         </is>
       </c>
     </row>
@@ -1498,12 +1498,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'id':_5,_'label':_'half-up'}</t>
+          <t>half-up</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'id': 5, 'label': 'Half-up'}</t>
+          <t>Half-up</t>
         </is>
       </c>
     </row>
@@ -1515,12 +1515,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'id':_6,_'label':_'half-up_with_veil'}</t>
+          <t>half-up_with_veil</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'id': 6, 'label': 'Half-up with veil'}</t>
+          <t>Half-up with veil</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'bride'}</t>
+          <t>bride</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Bride'}</t>
+          <t>Bride</t>
         </is>
       </c>
     </row>
@@ -1549,12 +1549,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'groom'}</t>
+          <t>groom</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Groom'}</t>
+          <t>Groom</t>
         </is>
       </c>
     </row>
@@ -1566,12 +1566,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'bridesmaids'}</t>
+          <t>bridesmaids</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Bridesmaids'}</t>
+          <t>Bridesmaids</t>
         </is>
       </c>
     </row>
@@ -1583,12 +1583,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'flower_girl'}</t>
+          <t>flower_girl</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'Flower Girl'}</t>
+          <t>Flower Girl</t>
         </is>
       </c>
     </row>
@@ -1600,12 +1600,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>{'id':_5,_'label':_'maid_of_honor'}</t>
+          <t>maid_of_honor</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>{'id': 5, 'label': 'Maid of honor'}</t>
+          <t>Maid of honor</t>
         </is>
       </c>
     </row>
@@ -1617,12 +1617,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>{'id':_6,_'label':_'junior_bridesmaid'}</t>
+          <t>junior_bridesmaid</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>{'id': 6, 'label': 'Junior Bridesmaid'}</t>
+          <t>Junior Bridesmaid</t>
         </is>
       </c>
     </row>
@@ -1634,12 +1634,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>{'id':_7,_'label':_'senior_bridesmaids'}</t>
+          <t>senior_bridesmaids</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>{'id': 7, 'label': 'Senior Bridesmaids'}</t>
+          <t>Senior Bridesmaids</t>
         </is>
       </c>
     </row>
@@ -1651,12 +1651,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>{'id':_8,_'label':_'officiant'}</t>
+          <t>officiant</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>{'id': 8, 'label': 'Officiant'}</t>
+          <t>Officiant</t>
         </is>
       </c>
     </row>
@@ -1668,12 +1668,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>{'id':_9,_'label':_'reader'}</t>
+          <t>reader</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>{'id': 9, 'label': 'Reader'}</t>
+          <t>Reader</t>
         </is>
       </c>
     </row>
@@ -1685,12 +1685,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>{'id':_10,_'label':_'best_man'}</t>
+          <t>best_man</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>{'id': 10, 'label': 'Best Man'}</t>
+          <t>Best Man</t>
         </is>
       </c>
     </row>
@@ -1702,12 +1702,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>{'id':_11,_'label':_'groomsmen'}</t>
+          <t>groomsmen</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>{'id': 11, 'label': 'Groomsmen'}</t>
+          <t>Groomsmen</t>
         </is>
       </c>
     </row>
@@ -1719,148 +1719,148 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>{'id':_12,_'label':_'pageboys'}</t>
+          <t>pageboys</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>{'id': 12, 'label': 'Pageboys'}</t>
+          <t>Pageboys</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>makeup_services_choices</t>
+          <t>makeup_services_2_choices</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'airbrush'}</t>
+          <t>airbrush</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Airbrush'}</t>
+          <t>Airbrush</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>makeup_services_choices</t>
+          <t>makeup_services_2_choices</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'airbrush_highlight'}</t>
+          <t>airbrush_highlight</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Airbrush Highlight'}</t>
+          <t>Airbrush Highlight</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>makeup_services_choices</t>
+          <t>makeup_services_2_choices</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'airbrush_highlight_and_contour'}</t>
+          <t>airbrush_highlight_and_contour</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Airbrush Highlight and Contour'}</t>
+          <t>Airbrush Highlight and Contour</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>makeup_services_choices</t>
+          <t>makeup_services_2_choices</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'airbrush_makeup'}</t>
+          <t>airbrush_makeup</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'Airbrush Makeup'}</t>
+          <t>Airbrush Makeup</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>makeup_services_choices</t>
+          <t>makeup_services_2_choices</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>{'id':_5,_'label':_'bridal'}</t>
+          <t>bridal</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>{'id': 5, 'label': 'Bridal'}</t>
+          <t>Bridal</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>makeup_services_choices</t>
+          <t>makeup_services_2_choices</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>{'id':_6,_'label':_'bridal_touch_up'}</t>
+          <t>bridal_touch_up</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>{'id': 6, 'label': 'Bridal Touch Up'}</t>
+          <t>Bridal Touch Up</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>makeup_services_choices</t>
+          <t>makeup_services_2_choices</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>{'id':_7,_'label':_'bridal_and_contour'}</t>
+          <t>bridal_and_contour</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>{'id': 7, 'label': 'Bridal and Contour'}</t>
+          <t>Bridal and Contour</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>makeup_services_choices</t>
+          <t>makeup_services_2_choices</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>{'id':_8,_'label':_'bridal_and_highlight'}</t>
+          <t>bridal_and_highlight</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>{'id': 8, 'label': 'Bridal and Highlight'}</t>
+          <t>Bridal and Highlight</t>
         </is>
       </c>
     </row>
@@ -1872,12 +1872,12 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'email'}</t>
+          <t>email</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Email'}</t>
+          <t>Email</t>
         </is>
       </c>
     </row>
@@ -1889,12 +1889,12 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'phone'}</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Phone'}</t>
+          <t>Phone</t>
         </is>
       </c>
     </row>
@@ -1906,12 +1906,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'both'}</t>
+          <t>both</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Both'}</t>
+          <t>Both</t>
         </is>
       </c>
     </row>
@@ -1923,12 +1923,12 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'inquire_about_payment'}</t>
+          <t>inquire_about_payment</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Inquire about payment'}</t>
+          <t>Inquire about payment</t>
         </is>
       </c>
     </row>
@@ -1940,12 +1940,12 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'pay_online'}</t>
+          <t>pay_online</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Pay online'}</t>
+          <t>Pay online</t>
         </is>
       </c>
     </row>
@@ -1957,12 +1957,12 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'pay_by_check'}</t>
+          <t>pay_by_check</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Pay by check'}</t>
+          <t>Pay by check</t>
         </is>
       </c>
     </row>
@@ -1974,12 +1974,12 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'airbrush'}</t>
+          <t>airbrush</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Airbrush'}</t>
+          <t>Airbrush</t>
         </is>
       </c>
     </row>
@@ -1991,12 +1991,12 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'airbrush_highlight'}</t>
+          <t>airbrush_highlight</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Airbrush Highlight'}</t>
+          <t>Airbrush Highlight</t>
         </is>
       </c>
     </row>
@@ -2008,12 +2008,12 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'airbrush_highlight_and_contour'}</t>
+          <t>airbrush_highlight_and_contour</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Airbrush Highlight and Contour'}</t>
+          <t>Airbrush Highlight and Contour</t>
         </is>
       </c>
     </row>
@@ -2025,12 +2025,12 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'airbrush_makeup'}</t>
+          <t>airbrush_makeup</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'Airbrush Makeup'}</t>
+          <t>Airbrush Makeup</t>
         </is>
       </c>
     </row>
@@ -2042,12 +2042,12 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>{'id':_5,_'label':_'bridal'}</t>
+          <t>bridal</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>{'id': 5, 'label': 'Bridal'}</t>
+          <t>Bridal</t>
         </is>
       </c>
     </row>
@@ -2059,12 +2059,12 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>{'id':_6,_'label':_'bridal_touch_up'}</t>
+          <t>bridal_touch_up</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>{'id': 6, 'label': 'Bridal Touch Up'}</t>
+          <t>Bridal Touch Up</t>
         </is>
       </c>
     </row>
@@ -2076,12 +2076,12 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>{'id':_7,_'label':_'bridal_and_contour'}</t>
+          <t>bridal_and_contour</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>{'id': 7, 'label': 'Bridal and Contour'}</t>
+          <t>Bridal and Contour</t>
         </is>
       </c>
     </row>
@@ -2093,148 +2093,148 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>{'id':_8,_'label':_'bridal_and_highlight'}</t>
+          <t>bridal_and_highlight</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>{'id': 8, 'label': 'Bridal and Highlight'}</t>
+          <t>Bridal and Highlight</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>make_up_services_choices</t>
+          <t>make_up_services_2_choices</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'airbrush'}</t>
+          <t>airbrush</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Airbrush'}</t>
+          <t>Airbrush</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>make_up_services_choices</t>
+          <t>make_up_services_2_choices</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'airbrush_highlight'}</t>
+          <t>airbrush_highlight</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Airbrush Highlight'}</t>
+          <t>Airbrush Highlight</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>make_up_services_choices</t>
+          <t>make_up_services_2_choices</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'airbrush_highlight_and_contour'}</t>
+          <t>airbrush_highlight_and_contour</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Airbrush Highlight and Contour'}</t>
+          <t>Airbrush Highlight and Contour</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>make_up_services_choices</t>
+          <t>make_up_services_2_choices</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'airbrush_makeup'}</t>
+          <t>airbrush_makeup</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'Airbrush Makeup'}</t>
+          <t>Airbrush Makeup</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>make_up_services_choices</t>
+          <t>make_up_services_2_choices</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>{'id':_5,_'label':_'bridal'}</t>
+          <t>bridal</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>{'id': 5, 'label': 'Bridal'}</t>
+          <t>Bridal</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>make_up_services_choices</t>
+          <t>make_up_services_2_choices</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>{'id':_6,_'label':_'bridal_touch_up'}</t>
+          <t>bridal_touch_up</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>{'id': 6, 'label': 'Bridal Touch Up'}</t>
+          <t>Bridal Touch Up</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>make_up_services_choices</t>
+          <t>make_up_services_2_choices</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>{'id':_7,_'label':_'bridal_and_contour'}</t>
+          <t>bridal_and_contour</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>{'id': 7, 'label': 'Bridal and Contour'}</t>
+          <t>Bridal and Contour</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>make_up_services_choices</t>
+          <t>make_up_services_2_choices</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>{'id':_8,_'label':_'bridal_and_highlight'}</t>
+          <t>bridal_and_highlight</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>{'id': 8, 'label': 'Bridal and Highlight'}</t>
+          <t>Bridal and Highlight</t>
         </is>
       </c>
     </row>
@@ -2246,12 +2246,12 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'airbrush'}</t>
+          <t>airbrush</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Airbrush'}</t>
+          <t>Airbrush</t>
         </is>
       </c>
     </row>
@@ -2263,12 +2263,12 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'airbrush_highlight'}</t>
+          <t>airbrush_highlight</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Airbrush Highlight'}</t>
+          <t>Airbrush Highlight</t>
         </is>
       </c>
     </row>
@@ -2280,12 +2280,12 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'airbrush_highlight_and_contour'}</t>
+          <t>airbrush_highlight_and_contour</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Airbrush Highlight and Contour'}</t>
+          <t>Airbrush Highlight and Contour</t>
         </is>
       </c>
     </row>
@@ -2297,12 +2297,12 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'airbrush_makeup'}</t>
+          <t>airbrush_makeup</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'Airbrush Makeup'}</t>
+          <t>Airbrush Makeup</t>
         </is>
       </c>
     </row>
@@ -2314,12 +2314,12 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>{'id':_5,_'label':_'bridal'}</t>
+          <t>bridal</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>{'id': 5, 'label': 'Bridal'}</t>
+          <t>Bridal</t>
         </is>
       </c>
     </row>
@@ -2331,12 +2331,12 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>{'id':_6,_'label':_'bridal_touch_up'}</t>
+          <t>bridal_touch_up</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>{'id': 6, 'label': 'Bridal Touch Up'}</t>
+          <t>Bridal Touch Up</t>
         </is>
       </c>
     </row>
@@ -2348,12 +2348,12 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>{'id':_7,_'label':_'bridal_and_contour'}</t>
+          <t>bridal_and_contour</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>{'id': 7, 'label': 'Bridal and Contour'}</t>
+          <t>Bridal and Contour</t>
         </is>
       </c>
     </row>
@@ -2365,12 +2365,12 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>{'id':_8,_'label':_'bridal_and_highlight'}</t>
+          <t>bridal_and_highlight</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>{'id': 8, 'label': 'Bridal and Highlight'}</t>
+          <t>Bridal and Highlight</t>
         </is>
       </c>
     </row>
@@ -2382,12 +2382,12 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'airbrush'}</t>
+          <t>airbrush</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Airbrush'}</t>
+          <t>Airbrush</t>
         </is>
       </c>
     </row>
@@ -2399,12 +2399,12 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'airbrush_highlight'}</t>
+          <t>airbrush_highlight</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Airbrush Highlight'}</t>
+          <t>Airbrush Highlight</t>
         </is>
       </c>
     </row>
@@ -2416,12 +2416,12 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'airbrush_highlight_and_contour'}</t>
+          <t>airbrush_highlight_and_contour</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Airbrush Highlight and Contour'}</t>
+          <t>Airbrush Highlight and Contour</t>
         </is>
       </c>
     </row>
@@ -2433,12 +2433,12 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'airbrush_makeup'}</t>
+          <t>airbrush_makeup</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'Airbrush Makeup'}</t>
+          <t>Airbrush Makeup</t>
         </is>
       </c>
     </row>
@@ -2450,12 +2450,12 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>{'id':_5,_'label':_'bridal'}</t>
+          <t>bridal</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>{'id': 5, 'label': 'Bridal'}</t>
+          <t>Bridal</t>
         </is>
       </c>
     </row>
@@ -2467,12 +2467,12 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>{'id':_6,_'label':_'bridal_touch_up'}</t>
+          <t>bridal_touch_up</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>{'id': 6, 'label': 'Bridal Touch Up'}</t>
+          <t>Bridal Touch Up</t>
         </is>
       </c>
     </row>
@@ -2484,12 +2484,12 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>{'id':_7,_'label':_'bridal_and_contour'}</t>
+          <t>bridal_and_contour</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>{'id': 7, 'label': 'Bridal and Contour'}</t>
+          <t>Bridal and Contour</t>
         </is>
       </c>
     </row>
@@ -2501,12 +2501,12 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>{'id':_8,_'label':_'bridal_and_highlight'}</t>
+          <t>bridal_and_highlight</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>{'id': 8, 'label': 'Bridal and Highlight'}</t>
+          <t>Bridal and Highlight</t>
         </is>
       </c>
     </row>
@@ -2518,12 +2518,12 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'airbrush'}</t>
+          <t>airbrush</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Airbrush'}</t>
+          <t>Airbrush</t>
         </is>
       </c>
     </row>
@@ -2535,12 +2535,12 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'airbrush_highlight'}</t>
+          <t>airbrush_highlight</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Airbrush Highlight'}</t>
+          <t>Airbrush Highlight</t>
         </is>
       </c>
     </row>
@@ -2552,12 +2552,12 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'airbrush_highlight_and_contour'}</t>
+          <t>airbrush_highlight_and_contour</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Airbrush Highlight and Contour'}</t>
+          <t>Airbrush Highlight and Contour</t>
         </is>
       </c>
     </row>
@@ -2569,12 +2569,12 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'airbrush_makeup'}</t>
+          <t>airbrush_makeup</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'Airbrush Makeup'}</t>
+          <t>Airbrush Makeup</t>
         </is>
       </c>
     </row>
@@ -2586,12 +2586,12 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>{'id':_5,_'label':_'bridal'}</t>
+          <t>bridal</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>{'id': 5, 'label': 'Bridal'}</t>
+          <t>Bridal</t>
         </is>
       </c>
     </row>
@@ -2603,12 +2603,12 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>{'id':_6,_'label':_'bridal_touch_up'}</t>
+          <t>bridal_touch_up</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>{'id': 6, 'label': 'Bridal Touch Up'}</t>
+          <t>Bridal Touch Up</t>
         </is>
       </c>
     </row>
@@ -2620,12 +2620,12 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>{'id':_7,_'label':_'bridal_and_contour'}</t>
+          <t>bridal_and_contour</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>{'id': 7, 'label': 'Bridal and Contour'}</t>
+          <t>Bridal and Contour</t>
         </is>
       </c>
     </row>
@@ -2637,12 +2637,12 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>{'id':_8,_'label':_'bridal_and_highlight'}</t>
+          <t>bridal_and_highlight</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>{'id': 8, 'label': 'Bridal and Highlight'}</t>
+          <t>Bridal and Highlight</t>
         </is>
       </c>
     </row>
@@ -2654,12 +2654,12 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'airbrush'}</t>
+          <t>airbrush</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Airbrush'}</t>
+          <t>Airbrush</t>
         </is>
       </c>
     </row>
@@ -2671,12 +2671,12 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'airbrush_highlight'}</t>
+          <t>airbrush_highlight</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Airbrush Highlight'}</t>
+          <t>Airbrush Highlight</t>
         </is>
       </c>
     </row>
@@ -2688,12 +2688,12 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'airbrush_highlight_and_contour'}</t>
+          <t>airbrush_highlight_and_contour</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Airbrush Highlight and Contour'}</t>
+          <t>Airbrush Highlight and Contour</t>
         </is>
       </c>
     </row>
@@ -2705,12 +2705,12 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'airbrush_makeup'}</t>
+          <t>airbrush_makeup</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'Airbrush Makeup'}</t>
+          <t>Airbrush Makeup</t>
         </is>
       </c>
     </row>
@@ -2722,12 +2722,12 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>{'id':_5,_'label':_'bridal'}</t>
+          <t>bridal</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>{'id': 5, 'label': 'Bridal'}</t>
+          <t>Bridal</t>
         </is>
       </c>
     </row>
@@ -2739,12 +2739,12 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>{'id':_6,_'label':_'bridal_touch_up'}</t>
+          <t>bridal_touch_up</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>{'id': 6, 'label': 'Bridal Touch Up'}</t>
+          <t>Bridal Touch Up</t>
         </is>
       </c>
     </row>
@@ -2756,12 +2756,12 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>{'id':_7,_'label':_'bridal_and_contour'}</t>
+          <t>bridal_and_contour</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>{'id': 7, 'label': 'Bridal and Contour'}</t>
+          <t>Bridal and Contour</t>
         </is>
       </c>
     </row>
@@ -2773,12 +2773,12 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>{'id':_8,_'label':_'bridal_and_highlight'}</t>
+          <t>bridal_and_highlight</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>{'id': 8, 'label': 'Bridal and Highlight'}</t>
+          <t>Bridal and Highlight</t>
         </is>
       </c>
     </row>
@@ -2790,12 +2790,12 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'airbrush'}</t>
+          <t>airbrush</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Airbrush'}</t>
+          <t>Airbrush</t>
         </is>
       </c>
     </row>
@@ -2807,12 +2807,12 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'airbrush_highlight'}</t>
+          <t>airbrush_highlight</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Airbrush Highlight'}</t>
+          <t>Airbrush Highlight</t>
         </is>
       </c>
     </row>
@@ -2824,12 +2824,12 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'airbrush_highlight_and_contour'}</t>
+          <t>airbrush_highlight_and_contour</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Airbrush Highlight and Contour'}</t>
+          <t>Airbrush Highlight and Contour</t>
         </is>
       </c>
     </row>
@@ -2841,12 +2841,12 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'airbrush_makeup'}</t>
+          <t>airbrush_makeup</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'Airbrush Makeup'}</t>
+          <t>Airbrush Makeup</t>
         </is>
       </c>
     </row>
@@ -2858,12 +2858,12 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>{'id':_5,_'label':_'bridal'}</t>
+          <t>bridal</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>{'id': 5, 'label': 'Bridal'}</t>
+          <t>Bridal</t>
         </is>
       </c>
     </row>
@@ -2875,12 +2875,12 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>{'id':_6,_'label':_'bridal_touch_up'}</t>
+          <t>bridal_touch_up</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>{'id': 6, 'label': 'Bridal Touch Up'}</t>
+          <t>Bridal Touch Up</t>
         </is>
       </c>
     </row>
@@ -2892,12 +2892,12 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>{'id':_7,_'label':_'bridal_and_contour'}</t>
+          <t>bridal_and_contour</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>{'id': 7, 'label': 'Bridal and Contour'}</t>
+          <t>Bridal and Contour</t>
         </is>
       </c>
     </row>
@@ -2909,12 +2909,12 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>{'id':_8,_'label':_'bridal_and_highlight'}</t>
+          <t>bridal_and_highlight</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>{'id': 8, 'label': 'Bridal and Highlight'}</t>
+          <t>Bridal and Highlight</t>
         </is>
       </c>
     </row>
@@ -2926,12 +2926,12 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'airbrush'}</t>
+          <t>airbrush</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Airbrush'}</t>
+          <t>Airbrush</t>
         </is>
       </c>
     </row>
@@ -2943,12 +2943,12 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'airbrush_highlight'}</t>
+          <t>airbrush_highlight</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Airbrush Highlight'}</t>
+          <t>Airbrush Highlight</t>
         </is>
       </c>
     </row>
@@ -2960,12 +2960,12 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'airbrush_highlight_and_contour'}</t>
+          <t>airbrush_highlight_and_contour</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Airbrush Highlight and Contour'}</t>
+          <t>Airbrush Highlight and Contour</t>
         </is>
       </c>
     </row>
@@ -2977,12 +2977,12 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'airbrush_makeup'}</t>
+          <t>airbrush_makeup</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'Airbrush Makeup'}</t>
+          <t>Airbrush Makeup</t>
         </is>
       </c>
     </row>
@@ -2994,12 +2994,12 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>{'id':_5,_'label':_'bridal'}</t>
+          <t>bridal</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>{'id': 5, 'label': 'Bridal'}</t>
+          <t>Bridal</t>
         </is>
       </c>
     </row>
@@ -3011,12 +3011,12 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>{'id':_6,_'label':_'bridal_touch_up'}</t>
+          <t>bridal_touch_up</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>{'id': 6, 'label': 'Bridal Touch Up'}</t>
+          <t>Bridal Touch Up</t>
         </is>
       </c>
     </row>
@@ -3028,12 +3028,12 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>{'id':_7,_'label':_'bridal_and_contour'}</t>
+          <t>bridal_and_contour</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>{'id': 7, 'label': 'Bridal and Contour'}</t>
+          <t>Bridal and Contour</t>
         </is>
       </c>
     </row>
@@ -3045,12 +3045,12 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>{'id':_8,_'label':_'bridal_and_highlight'}</t>
+          <t>bridal_and_highlight</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>{'id': 8, 'label': 'Bridal and Highlight'}</t>
+          <t>Bridal and Highlight</t>
         </is>
       </c>
     </row>
